--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487890_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487890_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.39</v>
+        <v>4.6908</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8705</v>
+        <v>3.4356</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5195</v>
+        <v>1.2553</v>
       </c>
       <c r="G2" t="n">
         <v>2.3507</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1413</v>
+        <v>1.4422</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6213</v>
+        <v>1.1864</v>
       </c>
       <c r="U2" t="n">
-        <v>0.52</v>
+        <v>0.2558</v>
       </c>
       <c r="V2" t="n">
         <v>0.6899</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5056</v>
+        <v>4.1678</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9629</v>
+        <v>3.0877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5427</v>
+        <v>1.0801</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4044</v>
+        <v>4.1996</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7417</v>
+        <v>3.7228</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3373</v>
+        <v>0.4768</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4291</v>
+        <v>4.9346</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2724</v>
+        <v>3.6413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1568</v>
+        <v>1.2932</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0247</v>
+        <v>-0.735</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4693</v>
+        <v>0.0814</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.494</v>
+        <v>-0.8164</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0793</v>
+        <v>0.5926</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2175</v>
+        <v>0.2343</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8619</v>
+        <v>0.3582</v>
       </c>
       <c r="V3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.309</v>
+        <v>3.055</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5519</v>
+        <v>0.7669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7571</v>
+        <v>2.2882</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1996</v>
+        <v>3.896</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7228</v>
+        <v>1.9782</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4768</v>
+        <v>1.9178</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9346</v>
+        <v>3.3328</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6413</v>
+        <v>0.9905</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2932</v>
+        <v>2.3423</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.735</v>
+        <v>0.5632</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0814</v>
+        <v>0.9877</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8164</v>
+        <v>-0.4245</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2662</v>
+        <v>1.0321</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3014</v>
+        <v>0.5558</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0353</v>
+        <v>0.4763</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1761</v>
+        <v>2.0705</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6969</v>
+        <v>-0.1444</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4793</v>
+        <v>2.2149</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2505</v>
+        <v>0.5515</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3818</v>
+        <v>2.6783</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8687</v>
+        <v>-2.1268</v>
       </c>
       <c r="J5" t="n">
-        <v>1.418</v>
+        <v>0.3761</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3004</v>
+        <v>1.4007</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176</v>
+        <v>-1.0246</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8325</v>
+        <v>0.1754</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0814</v>
+        <v>1.2776</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7511</v>
+        <v>-1.1022</v>
       </c>
       <c r="P5" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7799</v>
+        <v>0.8946</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1926</v>
+        <v>0.5201</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5874</v>
+        <v>0.3745</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9709</v>
+        <v>2.0538</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9626</v>
+        <v>1.5699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9917</v>
+        <v>0.484</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3643</v>
+        <v>0.4044</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7568</v>
+        <v>1.7417</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1211</v>
+        <v>-1.3373</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8727</v>
+        <v>1.4291</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7159</v>
+        <v>1.2724</v>
       </c>
       <c r="L6" t="n">
         <v>0.1568</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.237</v>
+        <v>-1.0247</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0408</v>
+        <v>0.4693</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2778</v>
+        <v>-1.494</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0022</v>
+        <v>1.6276</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5031</v>
+        <v>0.8244</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4991</v>
+        <v>0.8032</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6275</v>
+        <v>1.3975</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7574</v>
+        <v>1.9269</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8478</v>
+        <v>0.9802</v>
       </c>
       <c r="G7" t="n">
-        <v>3.896</v>
+        <v>2.2505</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9782</v>
+        <v>1.3818</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9178</v>
+        <v>0.8687</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3328</v>
+        <v>1.418</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9905</v>
+        <v>1.3004</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3423</v>
+        <v>0.1176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5632</v>
+        <v>0.8325</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9877</v>
+        <v>0.0814</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4245</v>
+        <v>0.7511</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8731</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2655</v>
+        <v>1.5307</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3014</v>
+        <v>0.4425</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0359</v>
+        <v>1.0883</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0373</v>
+        <v>1.5247</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3389</v>
+        <v>0.0897</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3763</v>
+        <v>1.435</v>
       </c>
       <c r="G8" t="n">
         <v>0.0417</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0144</v>
+        <v>0.5017</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4319</v>
+        <v>-0.0033</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4463</v>
+        <v>0.505</v>
       </c>
       <c r="V8" t="n">
         <v>1.3975</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8312</v>
+        <v>1.2655</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8965</v>
+        <v>2.4921</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0653</v>
+        <v>-1.2266</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3287</v>
+        <v>-0.3643</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3539</v>
+        <v>1.7568</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6826</v>
+        <v>-2.1211</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0799</v>
+        <v>0.8727</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3498</v>
+        <v>0.7159</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4297</v>
+        <v>0.1568</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7512</v>
+        <v>-1.237</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0041</v>
+        <v>1.0408</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.747</v>
+        <v>-2.2778</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1624</v>
+        <v>1.2968</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1833</v>
+        <v>1.0325</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0209</v>
+        <v>0.2643</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7472</v>
+        <v>1.2375</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.174</v>
+        <v>2.2832</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9213</v>
+        <v>-1.0458</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5515</v>
+        <v>1.3287</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6783</v>
+        <v>-0.3539</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1268</v>
+        <v>1.6826</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3761</v>
+        <v>2.0799</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4007</v>
+        <v>-0.3498</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0246</v>
+        <v>2.4297</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1754</v>
+        <v>-0.7512</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2776</v>
+        <v>-0.0041</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1022</v>
+        <v>-0.747</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4286</v>
+        <v>0.2438</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.2034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0509</v>
+        <v>0.8717</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5839</v>
+        <v>-1.0283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533</v>
+        <v>1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0404</v>
+        <v>-0.1857</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6119</v>
+        <v>1.5288</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5715</v>
+        <v>-1.7145</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3882</v>
+        <v>-0.3121</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3262</v>
+        <v>0.586</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7144</v>
+        <v>-0.8981</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4286</v>
+        <v>0.1264</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2857</v>
+        <v>0.9428</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1429</v>
+        <v>-0.8164</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2081</v>
+        <v>2.2893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2995</v>
+        <v>0.9762</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1957</v>
+        <v>0.3244</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1037</v>
+        <v>0.6518</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0699</v>
+        <v>0.115</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0579</v>
+        <v>-0.4767</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9881</v>
+        <v>0.5917</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1857</v>
+        <v>0.0404</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5288</v>
+        <v>0.6119</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7145</v>
+        <v>-0.5715</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3121</v>
+        <v>-0.3882</v>
       </c>
       <c r="K12" t="n">
-        <v>0.586</v>
+        <v>0.3262</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8981</v>
+        <v>-0.7144</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1264</v>
+        <v>0.4286</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9428</v>
+        <v>0.2857</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8164</v>
+        <v>0.1429</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0346</v>
+        <v>-0.1336</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7053</v>
+        <v>-0.0886</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7399</v>
+        <v>-0.045</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.6039</v>
+        <v>22.9792</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6962</v>
+        <v>13.0225</v>
       </c>
       <c r="F13" t="n">
-        <v>9.908100000000001</v>
+        <v>9.956999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>14.5135</v>
@@ -1441,7 +1441,7 @@
         <v>-3.9188</v>
       </c>
       <c r="J13" t="n">
-        <v>16.5357</v>
+        <v>16.53569999999999</v>
       </c>
       <c r="K13" t="n">
         <v>12.821</v>
@@ -1459,7 +1459,7 @@
         <v>-7.633299999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.609</v>
@@ -1468,13 +1468,13 @@
         <v>15.6088</v>
       </c>
       <c r="S13" t="n">
-        <v>9.6295</v>
+        <v>10.0047</v>
       </c>
       <c r="T13" t="n">
-        <v>4.9059</v>
+        <v>5.2319</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7239</v>
+        <v>4.7729</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5389</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4176</v>
+        <v>3.0488</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5719</v>
+        <v>5.2148</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1542</v>
+        <v>-2.166</v>
       </c>
       <c r="G14" t="n">
         <v>2.5592</v>
@@ -1546,13 +1546,13 @@
         <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9552</v>
+        <v>-1.3241</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3577</v>
+        <v>-0.7148</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5975</v>
+        <v>-0.6093</v>
       </c>
       <c r="V14" t="n">
         <v>1.3975</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.52</v>
+        <v>1.1691</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5441</v>
+        <v>1.2226</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0241</v>
+        <v>-0.0535</v>
       </c>
       <c r="G15" t="n">
         <v>0.4213</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8905</v>
+        <v>0.5397</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5839</v>
+        <v>0.2624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3066</v>
+        <v>0.2773</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4319</v>
+        <v>1.1502</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0738</v>
+        <v>1.5024</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6419</v>
+        <v>-0.3523</v>
       </c>
       <c r="G16" t="n">
         <v>1.9866</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3466</v>
+        <v>-0.6283</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8358</v>
+        <v>-0.4071</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5108</v>
+        <v>-0.2211</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3933</v>
+        <v>0.4418</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5238</v>
+        <v>0.4651</v>
       </c>
       <c r="G17" t="n">
         <v>0.2367</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1566</v>
+        <v>0.205</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2871</v>
+        <v>0.2284</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.484</v>
+        <v>-0.2888</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2883</v>
+        <v>-0.2002</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2041</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2799</v>
+        <v>-0.0847</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0842</v>
+        <v>0.0039</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2396</v>
+        <v>-1.2713</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3395</v>
+        <v>0.1963</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9001</v>
+        <v>-1.4675</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6321</v>
@@ -1936,13 +1936,13 @@
         <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2319</v>
+        <v>-1.2636</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2925</v>
+        <v>-0.7567</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9394</v>
+        <v>-0.5069</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3904</v>
+        <v>-3.084</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.199</v>
+        <v>-2.4133</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1913</v>
+        <v>-0.6707</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9599</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8873</v>
+        <v>-0.581</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3295</v>
+        <v>-0.5438</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5578</v>
+        <v>-0.0372</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.655</v>
+        <v>-4.0861</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1079</v>
+        <v>-0.858</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5471</v>
+        <v>-3.2281</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8619</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7307</v>
+        <v>-1.1618</v>
       </c>
       <c r="T21" t="n">
-        <v>0.332</v>
+        <v>-0.4181</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0627</v>
+        <v>-0.7437</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8137</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.677</v>
+        <v>-4.9468</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3923</v>
+        <v>-4.6844</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2847</v>
+        <v>-0.2624</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.6767</v>
+        <v>-4.8503</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.8146</v>
+        <v>-5.8872</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8621</v>
+        <v>1.0369</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9904</v>
+        <v>-2.6619</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2671</v>
+        <v>-4.6213</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7234</v>
+        <v>1.9594</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6863</v>
+        <v>-2.1884</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5475</v>
+        <v>-1.2659</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1388</v>
+        <v>-0.9225</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0812</v>
+        <v>2.7055</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7078</v>
+        <v>-1.3016</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.9819</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0521</v>
+        <v>-0.3196</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7076</v>
+        <v>-0.4599</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6275</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.258</v>
+        <v>-4.9872</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6844</v>
+        <v>-3.6066</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5736</v>
+        <v>-1.3806</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.8503</v>
+        <v>-4.6767</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.8872</v>
+        <v>-3.8146</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0369</v>
+        <v>-0.8621</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6619</v>
+        <v>-2.9904</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.6213</v>
+        <v>-2.2671</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9594</v>
+        <v>-0.7234</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1884</v>
+        <v>-1.6863</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2659</v>
+        <v>-1.5475</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9225</v>
+        <v>-0.1388</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7055</v>
+        <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6127</v>
+        <v>-1.0181</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9819</v>
+        <v>-0.87</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6308</v>
+        <v>-0.148</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4599</v>
+        <v>0.7076</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4599</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6629</v>
+        <v>-7.6066</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0484</v>
+        <v>-6.3698</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6145</v>
+        <v>-1.2368</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5324</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9245</v>
+        <v>-0.8682</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1396</v>
+        <v>-0.1819</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.064</v>
+        <v>-0.6863</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4599</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.6041</v>
+        <v>-20.4609</v>
       </c>
       <c r="E25" t="n">
         <v>-9.9079</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.696</v>
+        <v>-10.553</v>
       </c>
       <c r="G25" t="n">
         <v>-14.5136</v>
@@ -2404,13 +2404,13 @@
         <v>15.6088</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.629499999999998</v>
+        <v>-7.486700000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.723800000000001</v>
+        <v>-4.7238</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.9056</v>
+        <v>-2.7625</v>
       </c>
       <c r="V25" t="n">
         <v>1.5391</v>
